--- a/customers_raw.xlsx
+++ b/customers_raw.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="customers" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>Cust_ID</t>
   </si>
@@ -25,100 +25,70 @@
     <t>City</t>
   </si>
   <si>
-    <t>Signup Date</t>
-  </si>
-  <si>
     <t>Membership Tier</t>
   </si>
   <si>
-    <t>Rania Fassi</t>
-  </si>
-  <si>
-    <t>Adil Berrada</t>
-  </si>
-  <si>
-    <t>Mehdi Chaoui</t>
-  </si>
-  <si>
-    <t>Salma Idrissi</t>
-  </si>
-  <si>
-    <t>Youssef Ntifi</t>
-  </si>
-  <si>
-    <t>Imane Skalli</t>
-  </si>
-  <si>
-    <t>Karim Benjelloun</t>
-  </si>
-  <si>
-    <t>Nadia Ouazzani</t>
+    <t>Zineb Alaoui</t>
+  </si>
+  <si>
+    <t>Hamza Idrissi</t>
+  </si>
+  <si>
+    <t>Widad Bensouda</t>
+  </si>
+  <si>
+    <t>Anas Kettani</t>
+  </si>
+  <si>
+    <t>Ghita Lahlou</t>
+  </si>
+  <si>
+    <t>Reda Squalli</t>
+  </si>
+  <si>
+    <t>Nawal Tahiri</t>
+  </si>
+  <si>
+    <t>Younes Berrada</t>
+  </si>
+  <si>
+    <t>Samira Chafai</t>
   </si>
   <si>
     <t>Casablanca</t>
   </si>
   <si>
+    <t>RABAT</t>
+  </si>
+  <si>
+    <t>casablanca</t>
+  </si>
+  <si>
+    <t>Fes</t>
+  </si>
+  <si>
     <t>rabat</t>
   </si>
   <si>
-    <t>Fes</t>
-  </si>
-  <si>
-    <t>FES</t>
-  </si>
-  <si>
-    <t>Marrakech</t>
-  </si>
-  <si>
-    <t>casablanca</t>
+    <t>Tanger</t>
+  </si>
+  <si>
+    <t>tanger</t>
   </si>
   <si>
     <t>Rabat</t>
   </si>
   <si>
-    <t>Tanger</t>
-  </si>
-  <si>
-    <t>fes</t>
-  </si>
-  <si>
-    <t>2022-05-10</t>
-  </si>
-  <si>
-    <t>05/22/2022</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2023-01-20</t>
-  </si>
-  <si>
-    <t>2022-11-01</t>
-  </si>
-  <si>
-    <t>2022-08-14</t>
-  </si>
-  <si>
-    <t>2021-12-05</t>
-  </si>
-  <si>
-    <t>2023-03-30</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>silver</t>
-  </si>
-  <si>
     <t>Silver</t>
   </si>
   <si>
+    <t>gold</t>
+  </si>
+  <si>
     <t>Bronze</t>
-  </si>
-  <si>
-    <t>gold</t>
   </si>
   <si>
     <t>BRONZE</t>
@@ -453,10 +423,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,64 +439,52 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>301</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>201</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
-        <v>202</v>
+        <v>302</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
-        <v>203</v>
+        <v>303</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
-        <v>204</v>
+        <v>304</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -537,13 +495,10 @@
       <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
-        <v>205</v>
+        <v>305</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -552,106 +507,74 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
-        <v>206</v>
+        <v>306</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
-        <v>207</v>
+        <v>307</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9">
-        <v>208</v>
+        <v>308</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
-        <v>209</v>
+        <v>309</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>204</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
         <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
